--- a/03_Output/Models/Tables/Tab_Exposure_PO_cox_cesarea_stratified_IQR.xlsx
+++ b/03_Output/Models/Tables/Tab_Exposure_PO_cox_cesarea_stratified_IQR.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/jdconejeros_uc_cl/Documents/Research/Pollution_PerinatalOutcomes_Temuco26/03_Output/Models/Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_73EC80844B7BB3C930C643DAAB87B65CA24FC1E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87AE6A1C-57C3-0144-8DB8-E3078BD837AE}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_73EC80844B7BB3C930C643DAAB87B65CA24FC1E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC1D2D00-B8FC-F84C-9E8A-378C6939230E}"/>
   <bookViews>
-    <workbookView xWindow="-3840" yWindow="-21600" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1360" yWindow="-28800" windowWidth="51200" windowHeight="28800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spontaneous_IQR" sheetId="1" r:id="rId1"/>
     <sheet name="Cesarean_IQR" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Cesarean_IQR!$A$1:$N$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Spontaneous_IQR!$A$1:$N$6</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -793,6 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -848,7 +853,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1069,12 +1074,23 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N6" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Overall"/>
+        <filter val="T1"/>
+        <filter val="T2"/>
+        <filter val="T3"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1130,7 +1146,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1351,6 +1367,16 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N6" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Overall"/>
+        <filter val="T1"/>
+        <filter val="T2"/>
+        <filter val="T3"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>